--- a/Stock_OneClick/history/scan_result_20260527_204732.xlsx
+++ b/Stock_OneClick/history/scan_result_20260527_204732.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -635,24 +635,6 @@
       <c r="J3" t="n">
         <v>179.83</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-27; 相对D0=-0.91%; 本次触发=2026-05-27(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
@@ -704,24 +686,6 @@
       <c r="J4" t="n">
         <v>16.46</v>
       </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-27; 相对D0=2.11%; 本次触发=2026-05-27(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
@@ -773,24 +737,12 @@
       <c r="J5" s="5" t="n">
         <v>266.89</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-27; 相对D0=1.77%; 本次触发=2026-05-27(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-05-27</t>
@@ -842,27 +794,15 @@
       <c r="J6" s="5" t="n">
         <v>89.06999999999999</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>D0=85.42; 最新=2026-05-27; 相对D0=4.27%; 本次触发=2026-05-27(正式买入 | 第一买入点 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
+          <t>D0=85.42; 最新=2026-05-27; 相对D0=4.27%; 本次触发=2026-05-27(正式买入 | 第一观察点 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
         </is>
       </c>
     </row>
@@ -911,24 +851,12 @@
       <c r="J7" s="5" t="n">
         <v>271.85</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-05-27; 相对D0=0.00%; 本次触发=2026-05-27(正式买入 | 预警买入)</t>
@@ -980,24 +908,6 @@
       <c r="J8" t="n">
         <v>90.87</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-05-27; 相对D0=0.00%; 本次触发=2026-05-27(正式买入)</t>
@@ -1049,24 +959,6 @@
       <c r="J9" t="n">
         <v>41.35</v>
       </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>D0=41.35; 最新=2026-05-27; 相对D0=0.00%; 本次触发=2026-05-27(正式买入 | 预警买入)</t>
@@ -1118,24 +1010,12 @@
       <c r="J10" s="5" t="n">
         <v>102.12</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-05-27; 相对D0=0.00%; 本次触发=2026-05-27(预警买入)</t>
@@ -1187,24 +1067,6 @@
       <c r="J11" t="n">
         <v>190.96</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-05-27; 相对D0=0.00%; 本次触发=2026-05-27(预警买入)</t>
@@ -1256,24 +1118,12 @@
       <c r="J12" s="5" t="n">
         <v>198.95</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-27; 相对D0=-1.95%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1325,24 +1175,12 @@
       <c r="J13" s="5" t="n">
         <v>169.62</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-27; 相对D0=1.34%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1394,24 +1232,12 @@
       <c r="J14" s="5" t="n">
         <v>54.94</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-27; 相对D0=18.07%</t>
@@ -1463,24 +1289,12 @@
       <c r="J15" s="5" t="n">
         <v>177.51</v>
       </c>
-      <c r="K15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-27; 相对D0=-1.42%</t>
@@ -1532,24 +1346,12 @@
       <c r="J16" s="5" t="n">
         <v>47.66</v>
       </c>
-      <c r="K16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-27; 相对D0=-0.96%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1601,24 +1403,6 @@
       <c r="J17" t="n">
         <v>134.3</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-27; 相对D0=-4.90%</t>
@@ -1670,24 +1454,6 @@
       <c r="J18" t="n">
         <v>406.37</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-27; 相对D0=3.84%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1739,24 +1505,6 @@
       <c r="J19" t="n">
         <v>1031.89</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-27; 相对D0=-0.66%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1808,24 +1556,12 @@
       <c r="J20" s="5" t="n">
         <v>180.13</v>
       </c>
-      <c r="K20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-27; 相对D0=0.43%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -1877,24 +1613,12 @@
       <c r="J21" s="5" t="n">
         <v>294.46</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-27; 相对D0=-9.71%</t>
@@ -1946,24 +1670,6 @@
       <c r="J22" t="n">
         <v>23.72</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-27; 相对D0=5.38%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2015,24 +1721,12 @@
       <c r="J23" s="5" t="n">
         <v>246.47</v>
       </c>
-      <c r="K23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-27; 相对D0=6.24%</t>
@@ -2084,24 +1778,6 @@
       <c r="J24" t="n">
         <v>135.78</v>
       </c>
-      <c r="K24" t="n">
-        <v/>
-      </c>
-      <c r="L24" t="n">
-        <v/>
-      </c>
-      <c r="M24" t="n">
-        <v/>
-      </c>
-      <c r="N24" t="n">
-        <v/>
-      </c>
-      <c r="O24" t="n">
-        <v/>
-      </c>
-      <c r="P24" t="n">
-        <v/>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-27; 相对D0=4.05%</t>
@@ -2153,24 +1829,12 @@
       <c r="J25" s="5" t="n">
         <v>440.36</v>
       </c>
-      <c r="K25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-27; 相对D0=3.37%</t>
@@ -2222,24 +1886,12 @@
       <c r="J26" s="5" t="n">
         <v>13.44</v>
       </c>
-      <c r="K26" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
       <c r="Q26" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-27; 相对D0=3.23%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2291,24 +1943,12 @@
       <c r="J27" s="5" t="n">
         <v>72.19</v>
       </c>
-      <c r="K27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P27" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-05-27; 相对D0=-1.73%</t>
@@ -2360,24 +2000,6 @@
       <c r="J28" t="n">
         <v>421.86</v>
       </c>
-      <c r="K28" t="n">
-        <v/>
-      </c>
-      <c r="L28" t="n">
-        <v/>
-      </c>
-      <c r="M28" t="n">
-        <v/>
-      </c>
-      <c r="N28" t="n">
-        <v/>
-      </c>
-      <c r="O28" t="n">
-        <v/>
-      </c>
-      <c r="P28" t="n">
-        <v/>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-05-27; 相对D0=-0.04%</t>
@@ -2429,24 +2051,12 @@
       <c r="J29" s="5" t="n">
         <v>87.83</v>
       </c>
-      <c r="K29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-05-27; 相对D0=1.55%</t>
@@ -2498,24 +2108,12 @@
       <c r="J30" s="5" t="n">
         <v>107.44</v>
       </c>
-      <c r="K30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-05-27; 相对D0=-0.67%</t>
@@ -2567,24 +2165,6 @@
       <c r="J31" t="n">
         <v>104.27</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-05-27; 相对D0=-1.53%</t>
@@ -2636,24 +2216,6 @@
       <c r="J32" t="n">
         <v>85.44</v>
       </c>
-      <c r="K32" t="n">
-        <v/>
-      </c>
-      <c r="L32" t="n">
-        <v/>
-      </c>
-      <c r="M32" t="n">
-        <v/>
-      </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
-      <c r="O32" t="n">
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>D0=88.50; 最新=2026-05-27; 相对D0=-3.46%</t>
@@ -2705,24 +2267,6 @@
       <c r="J33" t="n">
         <v>142.14</v>
       </c>
-      <c r="K33" t="n">
-        <v/>
-      </c>
-      <c r="L33" t="n">
-        <v/>
-      </c>
-      <c r="M33" t="n">
-        <v/>
-      </c>
-      <c r="N33" t="n">
-        <v/>
-      </c>
-      <c r="O33" t="n">
-        <v/>
-      </c>
-      <c r="P33" t="n">
-        <v/>
-      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>D0=158.34; 最新=2026-05-27; 相对D0=-10.23%</t>
@@ -2774,24 +2318,12 @@
       <c r="J34" s="5" t="n">
         <v>388.83</v>
       </c>
-      <c r="K34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-05-27; 相对D0=-0.01%</t>
@@ -2843,24 +2375,12 @@
       <c r="J35" s="5" t="n">
         <v>635.255</v>
       </c>
-      <c r="K35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-05-27; 相对D0=3.74%</t>
@@ -2912,24 +2432,12 @@
       <c r="J36" s="5" t="n">
         <v>67.81999999999999</v>
       </c>
-      <c r="K36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-05-27; 相对D0=-1.28%</t>
@@ -2981,24 +2489,12 @@
       <c r="J37" s="5" t="n">
         <v>106.61</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-05-27; 相对D0=-0.31%</t>
@@ -3050,24 +2546,12 @@
       <c r="J38" s="5" t="n">
         <v>12.07</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-05-27; 相对D0=-1.23%</t>
@@ -3119,24 +2603,6 @@
       <c r="J39" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="K39" t="n">
-        <v/>
-      </c>
-      <c r="L39" t="n">
-        <v/>
-      </c>
-      <c r="M39" t="n">
-        <v/>
-      </c>
-      <c r="N39" t="n">
-        <v/>
-      </c>
-      <c r="O39" t="n">
-        <v/>
-      </c>
-      <c r="P39" t="n">
-        <v/>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-05-27; 相对D0=1.72%</t>
@@ -3188,24 +2654,12 @@
       <c r="J40" s="5" t="n">
         <v>18.35</v>
       </c>
-      <c r="K40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-05-27; 相对D0=-0.27%</t>
@@ -3256,24 +2710,6 @@
       </c>
       <c r="J41" t="n">
         <v>319.78</v>
-      </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3511,24 +2947,12 @@
       <c r="J53" s="5" t="n">
         <v>56.5</v>
       </c>
-      <c r="K53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-05-27; 相对D0=0.00%; 本次触发=2026-05-27(正式卖出 | 预警卖出)</t>
@@ -3580,24 +3004,12 @@
       <c r="J54" s="5" t="n">
         <v>126.41</v>
       </c>
-      <c r="K54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-05-27; 相对D0=0.00%; 本次触发=2026-05-27(正式卖出 | 预警卖出)</t>
@@ -3649,24 +3061,12 @@
       <c r="J55" s="5" t="n">
         <v>39.6</v>
       </c>
-      <c r="K55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P55" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="5" t="n"/>
       <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-27; 相对D0=-4.51%</t>
@@ -3718,24 +3118,12 @@
       <c r="J56" s="5" t="n">
         <v>90.87</v>
       </c>
-      <c r="K56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-05-27; 相对D0=0.25%</t>
@@ -3787,24 +3175,12 @@
       <c r="J57" s="5" t="n">
         <v>182.4</v>
       </c>
-      <c r="K57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P57" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-05-27; 相对D0=-1.25%</t>
@@ -3856,24 +3232,12 @@
       <c r="J58" s="5" t="n">
         <v>134.3</v>
       </c>
-      <c r="K58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P58" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
       <c r="Q58" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-05-27; 相对D0=-1.40%</t>
@@ -3925,24 +3289,12 @@
       <c r="J59" s="5" t="n">
         <v>41.35</v>
       </c>
-      <c r="K59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>D0=37.61; 最新=2026-05-27; 相对D0=9.94%</t>
@@ -3994,24 +3346,12 @@
       <c r="J60" s="5" t="n">
         <v>294.46</v>
       </c>
-      <c r="K60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-05-27; 相对D0=-4.19%</t>
@@ -4063,24 +3403,12 @@
       <c r="J61" s="5" t="n">
         <v>56.89</v>
       </c>
-      <c r="K61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P61" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-05-27; 相对D0=-0.99%</t>
@@ -4131,24 +3459,6 @@
       </c>
       <c r="J62" t="n">
         <v>13.28</v>
-      </c>
-      <c r="K62" t="n">
-        <v/>
-      </c>
-      <c r="L62" t="n">
-        <v/>
-      </c>
-      <c r="M62" t="n">
-        <v/>
-      </c>
-      <c r="N62" t="n">
-        <v/>
-      </c>
-      <c r="O62" t="n">
-        <v/>
-      </c>
-      <c r="P62" t="n">
-        <v/>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4246,7 +3556,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4258,7 +3567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4671,10 +3980,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6621,8 +5926,6 @@
       <c r="T22" t="b">
         <v>1</v>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=44.82; 4H分金=47.70</t>
@@ -7615,7 +6918,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -8086,7 +7389,6 @@
       <c r="D2" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="8" t="n">
         <v>46164</v>
       </c>
@@ -8138,7 +7440,6 @@
       <c r="D3" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="8" t="n">
         <v>46164</v>
       </c>
@@ -8344,7 +7645,6 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" s="8" t="n">
         <v>46169</v>
       </c>
@@ -8433,7 +7733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8829,7 +8129,6 @@
       <c r="I10" s="12" t="n">
         <v>-0.049002</v>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -9073,7 +8372,6 @@
       <c r="I16" s="13" t="n">
         <v>0.062371</v>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9111,7 +8409,6 @@
       <c r="I17" s="13" t="n">
         <v>0.04046</v>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -9233,7 +8530,6 @@
       <c r="I20" s="13" t="n">
         <v>0.033685</v>
       </c>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -9503,11 +8799,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9519,7 +8810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -9680,24 +8971,12 @@
       <c r="J3" s="5" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9749,24 +9028,12 @@
       <c r="J4" s="5" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9818,24 +9085,12 @@
       <c r="J5" s="5" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9887,24 +9142,12 @@
       <c r="J6" s="5" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9956,24 +9199,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10025,24 +9250,12 @@
       <c r="J8" s="5" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10094,24 +9307,12 @@
       <c r="J9" s="5" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10163,24 +9364,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10232,24 +9415,12 @@
       <c r="J11" s="5" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10301,24 +9472,12 @@
       <c r="J12" s="5" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10370,24 +9529,12 @@
       <c r="J13" s="5" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10439,24 +9586,12 @@
       <c r="J14" s="5" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10508,24 +9643,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10577,24 +9694,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10646,24 +9745,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10715,24 +9796,12 @@
       <c r="J18" s="5" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10784,24 +9853,12 @@
       <c r="J19" s="5" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10853,24 +9910,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10922,24 +9961,12 @@
       <c r="J21" s="5" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11176,24 +10203,12 @@
       <c r="J33" s="5" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -11238,11 +10253,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11254,7 +10264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -11378,7 +10388,6 @@
       <c r="G4" s="12" t="n">
         <v>-0.000355</v>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -11474,7 +10483,6 @@
       <c r="G7" s="12" t="n">
         <v>-0.015299</v>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -11622,7 +10630,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
@@ -11686,7 +10694,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
@@ -11730,7 +10738,6 @@
       <c r="G15" s="13" t="n">
         <v>0.01725</v>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -11794,7 +10801,6 @@
       <c r="G17" s="12" t="n">
         <v>-0.01275</v>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18"/>
     <row r="19">
@@ -12250,7 +11256,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
